--- a/output/pdf_financials_xlsx/LCE.xlsx
+++ b/output/pdf_financials_xlsx/LCE.xlsx
@@ -4803,40 +4803,40 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>2.883366</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>3.30933</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>3.30933</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>3.30933</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>3.30933</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>3.505295</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>3.514278</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.250057</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>10.851344</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>11.954561</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>12.59869</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>13.360055</v>
       </c>
     </row>
     <row r="93">
@@ -7982,7 +7982,11 @@
           <t>Reserves (Note 10)</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -9302,7 +9306,11 @@
           <t>Reserves (Note 11)</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>-</t>
@@ -10366,7 +10374,11 @@
           <t>Reserves (Note 14)</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>-</t>
@@ -11210,7 +11222,11 @@
           <t>Reserves (Note 8) 3,738,975</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>-</t>
@@ -12206,7 +12222,11 @@
           <t>Reserves (Note 8) 3,514,278</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
           <t>-</t>
@@ -12982,7 +13002,11 @@
           <t>Reserves (Note 8) 3,505,295</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
           <t>-</t>
@@ -13582,7 +13606,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>-</t>
@@ -13962,7 +13990,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>-</t>
@@ -14804,7 +14836,11 @@
           <t>Reserves (Note 8) 3,309,330</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E105" s="5" t="n">
         <v>2.883366</v>
       </c>

--- a/output/pdf_financials_xlsx/LCE.xlsx
+++ b/output/pdf_financials_xlsx/LCE.xlsx
@@ -957,16 +957,16 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.007636</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.011771</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.006203</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.01316</v>
       </c>
       <c r="F12" s="1" t="inlineStr">
         <is>
@@ -984,19 +984,19 @@
         </is>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.019663</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.518712</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.825472</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.412731</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.108814</v>
       </c>
     </row>
     <row r="13">
@@ -1776,16 +1776,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-3.185103</v>
+        <v>-3.192739</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.396182</v>
+        <v>-0.407953</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-7.763494</v>
+        <v>-7.769697</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.900343</v>
+        <v>-0.913503</v>
       </c>
       <c r="F27" s="1" t="inlineStr">
         <is>
@@ -1884,16 +1884,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-3.172578</v>
+        <v>-3.180214</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.379714</v>
+        <v>-0.391485</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-7.749899</v>
+        <v>-7.756102</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.89055</v>
+        <v>-0.90371</v>
       </c>
       <c r="F29" s="1" t="inlineStr">
         <is>
@@ -2146,22 +2146,22 @@
         <v>0</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.808489</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.271796</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.279003</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>1.279003</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.390855</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.007493</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>23.137155</v>
@@ -2232,22 +2232,22 @@
         <v>0</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.808489</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.271796</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.202392</v>
+        <v>1.481395</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.202392</v>
+        <v>1.481395</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.0945</v>
+        <v>0.485355</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.007493</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>23.161155</v>
@@ -2748,22 +2748,22 @@
         <v>3.545371</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.867883</v>
+        <v>0.059394</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.324436</v>
+        <v>0.05264</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.297717</v>
+        <v>0.018714</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.297717</v>
+        <v>0.018714</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.410296</v>
+        <v>0.019441</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.01407</v>
+        <v>0.006577</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>0.355501</v>
@@ -6354,19 +6354,19 @@
         </is>
       </c>
       <c r="I124" s="3" t="n">
-        <v>0</v>
+        <v>-0.028753</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>0</v>
+        <v>-0.345032</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>0</v>
+        <v>-0.345033</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>0</v>
+        <v>-0.344745</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.258895</v>
       </c>
     </row>
     <row r="125">
@@ -6403,19 +6403,19 @@
         </is>
       </c>
       <c r="I125" s="3" t="n">
-        <v>0</v>
+        <v>-0.028753</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>0</v>
+        <v>-0.345032</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>0</v>
+        <v>-0.345033</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>-0.344745</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.258895</v>
       </c>
     </row>
     <row r="126">
@@ -10522,7 +10522,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -11522,7 +11522,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -13156,7 +13156,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -16214,7 +16214,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
           <t>-</t>
@@ -21198,7 +21202,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -24928,7 +24932,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E241" s="5" t="n">
